--- a/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -9,58 +9,22 @@
     <x:sheet name="June 2025" sheetId="7" r:id="rId7"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -148,7 +112,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -175,12 +139,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -188,6 +146,27 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -202,13 +181,6 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -253,12 +225,12 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -270,14 +242,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -459,7 +431,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -470,183 +442,201 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -910,311 +900,287 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45809</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>45827.2931018519</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>45827.293125</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1435677</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>45827.2985763889</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H7" s="17">
         <x:v>45827.0419791667</x:v>
       </x:c>
-      <x:c r="I7" s="12">
+      <x:c r="I7" s="17">
         <x:v>45827.0420138889</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="16" t="n">
         <x:v>52268</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="n">
+      <x:c r="K7" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L7" s="17">
         <x:v>45827.0460069444</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="M7" s="16" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="19" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="19" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="19" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="20">
         <x:v>45826.1449768519</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="21">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="n">
+      <x:c r="J8" s="19" t="n">
         <x:v>1435666</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="22" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="20">
         <x:v>45826.2821412037</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>18</x:v>
+      <x:c r="M8" s="19" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
+      <x:c r="B9" s="19" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="19" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F9" s="19" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H9" s="20">
         <x:v>45827.1931712963</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="21">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J9" s="15" t="n">
+      <x:c r="J9" s="19" t="n">
         <x:v>1234312</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="22" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="20">
         <x:v>45827.2195833333</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>25</x:v>
+      <x:c r="M9" s="19" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
+      <x:c r="B12" s="23" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="24" t="s"/>
+      <x:c r="D12" s="24" t="s"/>
+      <x:c r="E12" s="25" t="s"/>
+      <x:c r="F12" s="25" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
-        <x:v>37</x:v>
+      <x:c r="B13" s="26" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="B14" s="29" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s"/>
+      <x:c r="D14" s="30" t="s"/>
+      <x:c r="E14" s="30" t="s"/>
+      <x:c r="F14" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="B15" s="29" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s"/>
+      <x:c r="D15" s="30" t="s"/>
+      <x:c r="E15" s="30" t="s"/>
+      <x:c r="F15" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="B16" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C17" s="30" t="s"/>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="30" t="s"/>
-      <x:c r="F17" s="31" t="n">
+      <x:c r="B17" s="32" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="s"/>
+      <x:c r="D17" s="33" t="s"/>
+      <x:c r="E17" s="33" t="s"/>
+      <x:c r="F17" s="34" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>PERMIT SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -902,7 +902,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45809</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -1120,72 +1120,72 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="23" t="s">
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="25" t="s"/>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="25" t="s"/>
     </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="26" t="s">
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="26" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="s">
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="s">
         <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="29" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="30" t="s"/>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="30" t="s"/>
-      <x:c r="F14" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="29" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C15" s="30" t="s"/>
-      <x:c r="D15" s="30" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="31" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
       <x:c r="B16" s="29" t="s">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C16" s="30" t="s"/>
       <x:c r="D16" s="30" t="s"/>
       <x:c r="E16" s="30" t="s"/>
       <x:c r="F16" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="29" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C17" s="30" t="s"/>
+      <x:c r="D17" s="30" t="s"/>
+      <x:c r="E17" s="30" t="s"/>
+      <x:c r="F17" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="32" t="s">
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="32" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C17" s="33" t="s"/>
-      <x:c r="D17" s="33" t="s"/>
-      <x:c r="E17" s="33" t="s"/>
-      <x:c r="F17" s="34" t="n">
+      <x:c r="C19" s="33" t="s"/>
+      <x:c r="D19" s="33" t="s"/>
+      <x:c r="E19" s="33" t="s"/>
+      <x:c r="F19" s="34" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2161,15 +2161,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+  <x:mergeCells count="9">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -509,7 +509,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -545,35 +545,35 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -590,6 +590,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -963,7 +967,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -1001,7 +1005,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>7</x:v>
@@ -1118,71 +1122,97 @@
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B10" s="23" t="s"/>
+      <x:c r="C10" s="23" t="s"/>
+      <x:c r="D10" s="23" t="s"/>
+      <x:c r="E10" s="23" t="s"/>
+      <x:c r="F10" s="23" t="s"/>
+      <x:c r="G10" s="23" t="s"/>
+      <x:c r="H10" s="23" t="s"/>
+      <x:c r="I10" s="23" t="s"/>
+      <x:c r="J10" s="23" t="s"/>
+      <x:c r="K10" s="23" t="s"/>
+      <x:c r="L10" s="23" t="s"/>
+      <x:c r="M10" s="23" t="s"/>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B11" s="23" t="s"/>
+      <x:c r="C11" s="23" t="s"/>
+      <x:c r="D11" s="23" t="s"/>
+      <x:c r="E11" s="23" t="s"/>
+      <x:c r="F11" s="23" t="s"/>
+      <x:c r="G11" s="23" t="s"/>
+      <x:c r="H11" s="23" t="s"/>
+      <x:c r="I11" s="23" t="s"/>
+      <x:c r="J11" s="23" t="s"/>
+      <x:c r="K11" s="23" t="s"/>
+      <x:c r="L11" s="23" t="s"/>
+      <x:c r="M11" s="23" t="s"/>
+    </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="24" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="25" t="s"/>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="26" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+      <x:c r="B15" s="27" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="s">
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="29" t="s">
+      <x:c r="B16" s="30" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="C16" s="31" t="s"/>
+      <x:c r="D16" s="31" t="s"/>
+      <x:c r="E16" s="31" t="s"/>
+      <x:c r="F16" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="29" t="s">
+      <x:c r="B17" s="30" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C17" s="30" t="s"/>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="30" t="s"/>
-      <x:c r="F17" s="31" t="n">
+      <x:c r="C17" s="31" t="s"/>
+      <x:c r="D17" s="31" t="s"/>
+      <x:c r="E17" s="31" t="s"/>
+      <x:c r="F17" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="29" t="s">
+      <x:c r="B18" s="30" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
+      <x:c r="C18" s="31" t="s"/>
+      <x:c r="D18" s="31" t="s"/>
+      <x:c r="E18" s="31" t="s"/>
+      <x:c r="F18" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="32" t="s">
+      <x:c r="B19" s="33" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C19" s="33" t="s"/>
-      <x:c r="D19" s="33" t="s"/>
-      <x:c r="E19" s="33" t="s"/>
-      <x:c r="F19" s="34" t="n">
+      <x:c r="C19" s="34" t="s"/>
+      <x:c r="D19" s="34" t="s"/>
+      <x:c r="E19" s="34" t="s"/>
+      <x:c r="F19" s="35" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -937,7 +937,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1005,7 +1005,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>7</x:v>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,9 +22,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <x:si>
     <x:t>PERMIT SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -112,7 +148,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -157,21 +193,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -181,6 +202,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -431,7 +459,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -442,74 +470,68 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -540,107 +562,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -939,18 +945,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -968,251 +962,263 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45827.2931018519</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45827.293125</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1435677</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45827.2985763889</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
+      <x:c r="I7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="s">
+      <x:c r="L7" s="10" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G7" s="16" t="s">
+      <x:c r="M7" s="10" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="H7" s="17">
-        <x:v>45827.0419791667</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>45827.0420138889</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>52268</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>45827.0460069444</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="19" t="s">
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="19" t="s">
+      <x:c r="F8" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
+      <x:c r="G8" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="H8" s="12">
+        <x:v>45827.2931018519</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45827.293125</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1435677</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45827.2985763889</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="H8" s="20">
-        <x:v>45826.1449768519</x:v>
-      </x:c>
-      <x:c r="I8" s="21">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J8" s="19" t="n">
-        <x:v>1435666</x:v>
-      </x:c>
-      <x:c r="K8" s="22" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
-        <x:v>45826.2821412037</x:v>
-      </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
+      <x:c r="B9" s="11" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
+      <x:c r="C9" s="11" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F9" s="19" t="s">
+      <x:c r="D9" s="11" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G9" s="19" t="s">
+      <x:c r="E9" s="11" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H9" s="20">
+      <x:c r="F9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45827.0419791667</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>45827.0420138889</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>52268</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45827.0460069444</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45826.1449768519</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="n">
+        <x:v>1435666</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>45826.2821412037</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>45827.1931712963</x:v>
       </x:c>
-      <x:c r="I9" s="21">
+      <x:c r="I11" s="17">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1234312</x:v>
       </x:c>
-      <x:c r="K9" s="22" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="19">
         <x:v>45827.2195833333</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B10" s="23" t="s"/>
-      <x:c r="C10" s="23" t="s"/>
-      <x:c r="D10" s="23" t="s"/>
-      <x:c r="E10" s="23" t="s"/>
-      <x:c r="F10" s="23" t="s"/>
-      <x:c r="G10" s="23" t="s"/>
-      <x:c r="H10" s="23" t="s"/>
-      <x:c r="I10" s="23" t="s"/>
-      <x:c r="J10" s="23" t="s"/>
-      <x:c r="K10" s="23" t="s"/>
-      <x:c r="L10" s="23" t="s"/>
-      <x:c r="M10" s="23" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B11" s="23" t="s"/>
-      <x:c r="C11" s="23" t="s"/>
-      <x:c r="D11" s="23" t="s"/>
-      <x:c r="E11" s="23" t="s"/>
-      <x:c r="F11" s="23" t="s"/>
-      <x:c r="G11" s="23" t="s"/>
-      <x:c r="H11" s="23" t="s"/>
-      <x:c r="I11" s="23" t="s"/>
-      <x:c r="J11" s="23" t="s"/>
-      <x:c r="K11" s="23" t="s"/>
-      <x:c r="L11" s="23" t="s"/>
-      <x:c r="M11" s="23" t="s"/>
+      <x:c r="M11" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="26" t="s"/>
+      <x:c r="B14" s="20" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="s">
-        <x:v>25</x:v>
+      <x:c r="B15" s="23" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="30" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="31" t="s"/>
-      <x:c r="F16" s="32" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="30" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C17" s="31" t="s"/>
-      <x:c r="D17" s="31" t="s"/>
-      <x:c r="E17" s="31" t="s"/>
-      <x:c r="F17" s="32" t="n">
+      <x:c r="B17" s="26" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C18" s="31" t="s"/>
-      <x:c r="D18" s="31" t="s"/>
-      <x:c r="E18" s="31" t="s"/>
-      <x:c r="F18" s="32" t="n">
+      <x:c r="B18" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="33" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C19" s="34" t="s"/>
-      <x:c r="D19" s="34" t="s"/>
-      <x:c r="E19" s="34" t="s"/>
-      <x:c r="F19" s="35" t="n">
+      <x:c r="B19" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C19" s="30" t="s"/>
+      <x:c r="D19" s="30" t="s"/>
+      <x:c r="E19" s="30" t="s"/>
+      <x:c r="F19" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -459,11 +459,14 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -531,7 +534,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -561,6 +564,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -895,7 +902,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45809</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -967,258 +976,258 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="12" t="s"/>
+      <x:c r="E8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45827.2931018519</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>45827.293125</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1435677</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="14" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45827.2985763889</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45827.0419791667</x:v>
       </x:c>
-      <x:c r="I9" s="12">
+      <x:c r="I9" s="13">
         <x:v>45827.0420138889</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>52268</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="14" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45827.0460069444</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="C10" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
+      <x:c r="D10" s="16" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="E10" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="H10" s="17">
         <x:v>45826.1449768519</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="18">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1435666</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="20">
         <x:v>45826.2821412037</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
+      <x:c r="M10" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="C11" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
+      <x:c r="D11" s="16" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="E11" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="F11" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="H11" s="17">
         <x:v>45827.1931712963</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="18">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1234312</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="19" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="20">
         <x:v>45827.2195833333</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
+      <x:c r="M11" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+      <x:c r="B14" s="21" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="23" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="B15" s="24" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="27" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="27" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+      <x:c r="B18" s="27" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C18" s="28" t="s"/>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="28" t="s"/>
+      <x:c r="F18" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="29" t="s">
+      <x:c r="B19" s="30" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C19" s="30" t="s"/>
-      <x:c r="D19" s="30" t="s"/>
-      <x:c r="E19" s="30" t="s"/>
-      <x:c r="F19" s="31" t="n">
+      <x:c r="C19" s="31" t="s"/>
+      <x:c r="D19" s="31" t="s"/>
+      <x:c r="E19" s="31" t="s"/>
+      <x:c r="F19" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,9 +22,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
-  <x:si>
-    <x:t>PERMIT SUMMARY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+  <x:si>
+    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMITS SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>III | June 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -148,7 +154,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -188,6 +194,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -459,17 +489,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -482,59 +518,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -565,95 +601,103 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -882,58 +926,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45809</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -976,258 +1020,258 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s"/>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="F8" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45827.2931018519</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="15">
         <x:v>45827.293125</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1435677</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>45827.2985763889</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>18</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="12" t="s">
+      <x:c r="D9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G9" s="12" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H9" s="13">
+      <x:c r="F9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>45827.0419791667</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="15">
         <x:v>45827.0420138889</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>52268</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="16" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L9" s="13">
+      <x:c r="L9" s="15">
         <x:v>45827.0460069444</x:v>
       </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>25</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="B10" s="17" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="C10" s="17" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="D10" s="18" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="E10" s="17" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>45826.1449768519</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="20">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1435666</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="21" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="22">
         <x:v>45826.2821412037</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>18</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="C11" s="17" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="D11" s="18" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="F11" s="17" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
         <x:v>45827.1931712963</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="20">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="18" t="n">
         <x:v>1234312</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="21" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="22">
         <x:v>45827.2195833333</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>25</x:v>
+      <x:c r="M11" s="17" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="23" t="s"/>
+      <x:c r="B14" s="23" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="25" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="s">
-        <x:v>37</x:v>
+      <x:c r="B15" s="26" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="B16" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="B17" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C17" s="30" t="s"/>
+      <x:c r="D17" s="30" t="s"/>
+      <x:c r="E17" s="30" t="s"/>
+      <x:c r="F17" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="27" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C18" s="28" t="s"/>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="28" t="s"/>
-      <x:c r="F18" s="29" t="n">
+      <x:c r="B18" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="30" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C19" s="31" t="s"/>
-      <x:c r="D19" s="31" t="s"/>
-      <x:c r="E19" s="31" t="s"/>
-      <x:c r="F19" s="32" t="n">
+      <x:c r="B19" s="32" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C19" s="33" t="s"/>
+      <x:c r="D19" s="33" t="s"/>
+      <x:c r="E19" s="33" t="s"/>
+      <x:c r="F19" s="34" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -2209,7 +2253,7 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -67,6 +67,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -151,10 +187,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -199,15 +237,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -223,15 +253,8 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -494,21 +517,21 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -518,59 +541,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -601,103 +624,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -926,78 +937,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1018,7 +1041,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1058,225 +1081,275 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45827.2931018519</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45827.293125</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1435677</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45827.2985763889</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45827.0419791667</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>45827.0420138889</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>52268</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45827.0460069444</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G10" s="17" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45827.2931018519</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45827.293125</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>1435677</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>45827.2985763889</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45826.1449768519</x:v>
-      </x:c>
-      <x:c r="I10" s="20">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1435666</x:v>
-      </x:c>
-      <x:c r="K10" s="21" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L10" s="22">
-        <x:v>45826.2821412037</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
+      <x:c r="B11" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D11" s="18" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E11" s="17" t="s">
+      <x:c r="C11" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F11" s="17" t="s">
+      <x:c r="D11" s="16" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G11" s="17" t="s">
+      <x:c r="E11" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H11" s="19">
+      <x:c r="F11" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>45827.0419791667</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45827.0420138889</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>52268</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>45827.0460069444</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>45826.1449768519</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1435666</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>45826.2821412037</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
         <x:v>45827.1931712963</x:v>
       </x:c>
-      <x:c r="I11" s="20">
+      <x:c r="I13" s="17">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
+      <x:c r="J13" s="16" t="n">
         <x:v>1234312</x:v>
       </x:c>
-      <x:c r="K11" s="21" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L11" s="22">
+      <x:c r="L13" s="19">
         <x:v>45827.2195833333</x:v>
       </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>27</x:v>
+      <x:c r="M13" s="15" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="25" t="s"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="20" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="22" t="s"/>
     </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C17" s="30" t="s"/>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="30" t="s"/>
-      <x:c r="F17" s="31" t="n">
-        <x:v>1</x:v>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="23" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="29" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
+      <x:c r="B18" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="32" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="s"/>
-      <x:c r="D19" s="33" t="s"/>
-      <x:c r="E19" s="33" t="s"/>
-      <x:c r="F19" s="34" t="n">
+    <x:row r="21" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B21" s="29" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s"/>
+      <x:c r="D21" s="30" t="s"/>
+      <x:c r="E21" s="30" t="s"/>
+      <x:c r="F21" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2250,16 +2323,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="10">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B14:F14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -67,42 +67,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -192,7 +156,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -236,14 +200,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -255,6 +211,21 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -512,7 +483,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -520,16 +491,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -541,13 +512,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -559,41 +524,50 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -624,28 +598,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -660,55 +626,71 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1041,7 +1023,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1081,275 +1063,225 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>45827.2931018519</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45827.293125</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1435677</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45827.2985763889</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="D9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="M8" s="9" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+      <x:c r="H9" s="15">
+        <x:v>45827.0419791667</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45827.0420138889</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>52268</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45827.0460069444</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="B10" s="17" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="C10" s="17" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="D10" s="18" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="E10" s="17" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45827.2931018519</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45827.293125</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1435677</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45827.2985763889</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="G10" s="17" t="s">
         <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
+        <x:v>45826.1449768519</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1435666</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="21">
+        <x:v>45826.2821412037</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="D11" s="18" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="F11" s="17" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="G11" s="17" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="H11" s="19">
+        <x:v>45827.1931712963</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>44197</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1234312</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>18810</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>45827.2195833333</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="24" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="25" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45827.0419791667</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45827.0420138889</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>52268</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45827.0460069444</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>45826.1449768519</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1435666</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>45826.2821412037</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>32</x:v>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>45827.1931712963</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>44197</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1234312</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>18810</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>45827.2195833333</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
-        <x:v>51</x:v>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="28" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
-        <x:v>1</x:v>
+      <x:c r="B18" s="28" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
-        <x:v>1</x:v>
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="31" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C19" s="32" t="s"/>
+      <x:c r="D19" s="32" t="s"/>
+      <x:c r="E19" s="32" t="s"/>
+      <x:c r="F19" s="33" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="29" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C21" s="30" t="s"/>
-      <x:c r="D21" s="30" t="s"/>
-      <x:c r="E21" s="30" t="s"/>
-      <x:c r="F21" s="31" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2328,12 +2260,12 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B16:F16"/>
+    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -84,6 +84,9 @@
     <x:t>61-6-2025-1055</x:t>
   </x:si>
   <x:si>
+    <x:t>1435677</x:t>
+  </x:si>
+  <x:si>
     <x:t>MANUELITO TOLENTINO</x:t>
   </x:si>
   <x:si>
@@ -105,6 +108,10 @@
     <x:t>61-6-2025-1050</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">
+52268</x:t>
+  </x:si>
+  <x:si>
     <x:t>cashier3 edge</x:t>
   </x:si>
   <x:si>
@@ -123,6 +130,9 @@
     <x:t>61-6-2025-1016</x:t>
   </x:si>
   <x:si>
+    <x:t>1435666</x:t>
+  </x:si>
+  <x:si>
     <x:t>PLAY STORE</x:t>
   </x:si>
   <x:si>
@@ -133,6 +143,9 @@
   </x:si>
   <x:si>
     <x:t>61-6-2025-1052</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234312</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -156,7 +169,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -225,13 +238,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
@@ -483,7 +489,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -524,50 +530,41 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -615,6 +612,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -626,71 +627,55 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1071,7 +1056,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
+      <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1081,202 +1066,202 @@
       <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45827.2931018519</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45827.293125</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1435677</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="H8" s="16">
+        <x:v>45827.2931036574</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45827.2931277431</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45827.2985763889</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45827.298578831</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="33.597656" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45827.0419791667</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>45827.0420138889</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>52268</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45827.0419894213</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45827.0420140278</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45827.0460069444</x:v>
+      <x:c r="L9" s="18">
+        <x:v>45827.0460181713</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G10" s="17" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45826.1449768519</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="E10" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45826.1449770949</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1435666</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45826.2821412037</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L10" s="18">
+        <x:v>45826.2821424653</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H11" s="19">
-        <x:v>45827.1931712963</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="D11" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45827.193172581</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1234312</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45827.2195833333</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>27</x:v>
+      <x:c r="L11" s="18">
+        <x:v>45827.2195876273</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="24" t="s"/>
+      <x:c r="B14" s="19" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="s">
-        <x:v>39</x:v>
+      <x:c r="B15" s="22" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="28" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="B17" s="25" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="B18" s="25" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="31" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C19" s="32" t="s"/>
-      <x:c r="D19" s="32" t="s"/>
-      <x:c r="E19" s="32" t="s"/>
-      <x:c r="F19" s="33" t="n">
+      <x:c r="B19" s="28" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -1008,7 +1008,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1048,7 +1048,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -1085,7 +1085,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="33.597656" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -1123,7 +1123,7 @@
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
@@ -1161,7 +1161,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>30</x:v>
       </x:c>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,15 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
   <x:si>
     <x:t>PERMITS SUMMARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>III | June 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -489,7 +486,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -506,6 +503,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -564,7 +564,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -600,6 +600,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -974,20 +978,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45809</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1010,258 +1014,258 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="16" t="s"/>
+      <x:c r="E8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45827.2931036574</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45827.2931277431</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45827.2931036574</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45827.2931277431</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45827.298578831</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45827.298578831</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="B9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="D9" s="16" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
+      <x:c r="E9" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45827.0419894213</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45827.0420140278</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45827.0419894213</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45827.0420140278</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>45827.0460181713</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>45827.0460181713</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
+      <x:c r="E10" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45826.1449770949</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45826.1449770949</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>45826.2821424653</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="F11" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="H11" s="17">
+        <x:v>45827.193172581</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>44197</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45827.193172581</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>44197</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>45827.2195876273</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>29</x:v>
+      <x:c r="M11" s="15" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="19" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="21" t="s"/>
+      <x:c r="B14" s="20" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="22" t="s">
+      <x:c r="B15" s="23" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="s">
-        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="B17" s="26" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
+      <x:c r="B18" s="26" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="B19" s="29" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C19" s="30" t="s"/>
+      <x:c r="D19" s="30" t="s"/>
+      <x:c r="E19" s="30" t="s"/>
+      <x:c r="F19" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -166,7 +166,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -206,14 +206,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -486,7 +478,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -497,16 +489,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -518,53 +507,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -599,87 +588,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -981,17 +966,17 @@
       <x:c r="B5" s="12">
         <x:v>45809</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1014,258 +999,258 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45827.2931036574</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45827.2931277431</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45827.298578831</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45827.0419894213</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45827.0420140278</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45827.0460181713</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45826.1449770949</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45826.2821424653</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45827.193172581</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45827.2195876273</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+      <x:c r="B14" s="19" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="29" t="s">
+      <x:c r="B19" s="28" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C19" s="30" t="s"/>
-      <x:c r="D19" s="30" t="s"/>
-      <x:c r="E19" s="30" t="s"/>
-      <x:c r="F19" s="31" t="n">
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -66,22 +66,25 @@
     <x:t>BY</x:t>
   </x:si>
   <x:si>
-    <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALEX C. LAGUISMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50-30 B Dña Isabel Avenue, Pulung Maragul, Angeles City, Pampanga</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AT-RSL-ROIII-1022-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1055</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1435677</x:t>
+    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JUAN DELA CRUZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Maimpis, City Of San Fernando (Capital), Pampanga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MP-ROIII-1003-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1435666</x:t>
   </x:si>
   <x:si>
     <x:t>MANUELITO TOLENTINO</x:t>
@@ -94,9 +97,6 @@
   </x:si>
   <x:si>
     <x:t>NEW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Maimpis, City Of San Fernando (Capital), Pampanga</x:t>
   </x:si>
   <x:si>
     <x:t>MP-ROIII-1005-25</x:t>
@@ -112,24 +112,6 @@
     <x:t>cashier3 edge</x:t>
   </x:si>
   <x:si>
-    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JUAN DELA CRUZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MP-ROIII-1003-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1435666</x:t>
-  </x:si>
-  <x:si>
     <x:t>PLAY STORE</x:t>
   </x:si>
   <x:si>
@@ -143,6 +125,24 @@
   </x:si>
   <x:si>
     <x:t>1234312</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALEX C. LAGUISMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50-30 B Dña Isabel Avenue, Pulung Maragul, Angeles City, Pampanga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AT-RSL-ROIII-1022-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1055</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1435677</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -1045,47 +1045,49 @@
       <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
+      <x:c r="D8" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>45827.2931036574</x:v>
+        <x:v>45826.1449770949</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>45827.2931277431</x:v>
+        <x:v>45826</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>130</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>45827.298578831</x:v>
+        <x:v>45826.2821424653</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
         <x:v>25</x:v>
@@ -1114,52 +1116,50 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="D10" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="16">
+        <x:v>45827.193172581</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>44197</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45826.1449770949</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="K10" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>18810</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>45826.2821424653</x:v>
+        <x:v>45827.2195876273</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="D11" s="15" t="s"/>
       <x:c r="E11" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
@@ -1170,22 +1170,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>45827.193172581</x:v>
+        <x:v>45827.2931036574</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>44197</x:v>
+        <x:v>45827.2931277431</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>18810</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>45827.2195876273</x:v>
+        <x:v>45827.298578831</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
@@ -1212,7 +1212,7 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
       <x:c r="B16" s="25" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C16" s="26" t="s"/>
       <x:c r="D16" s="26" t="s"/>
@@ -1223,7 +1223,7 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
       <x:c r="B17" s="25" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C17" s="26" t="s"/>
       <x:c r="D17" s="26" t="s"/>
@@ -1234,7 +1234,7 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
       <x:c r="B18" s="25" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="26" t="s"/>
       <x:c r="D18" s="26" t="s"/>
